--- a/Stage/Bedjou Ayoub fiche de synthése.xlsx
+++ b/Stage/Bedjou Ayoub fiche de synthése.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\portefolio\wetransfer_portfolio_2025-12-01_2312\Portfolio\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E722A1A8-DC51-4E5F-BEDC-2676D84E3412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF59A662-CB2A-4BB3-94DB-1A3AFE1C23A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -169,6 +169,15 @@
   </si>
   <si>
     <t>Mise en place et contrôle du matériel des salles de réunion</t>
+  </si>
+  <si>
+    <t>Création et administration de la base de données pour le site de l'association Aujourd'hui vers demain avec My SQL.</t>
+  </si>
+  <si>
+    <t>Maquettage et réalisation d'un site web pour l'association Aujourd'hui vers demain. Les fonctionnalités du site sont l'apprentissage de la langue française, l'aide aux devoirs, le dépôt de candidature en tant que bénévole et l'historique des activités. Les outils utilisés sont HTML, CSS,JS, PHP.</t>
+  </si>
+  <si>
+    <t>12/01/2026 au 20/02/2026</t>
   </si>
 </sst>
 </file>
@@ -241,18 +250,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -267,7 +270,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -372,51 +375,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
     <border diagonalDown="1">
       <left style="medium">
         <color theme="2" tint="-0.749992370372631"/>
@@ -658,7 +616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -681,23 +639,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -711,40 +663,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -759,28 +706,46 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -789,25 +754,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1154,90 +1100,93 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
-    <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="18.7109375" style="1" customWidth="1"/>
     <col min="9" max="43" width="11.42578125" customWidth="1"/>
     <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="30"/>
+      <c r="H1" s="27"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="48" t="s">
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="49"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="46"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="14" t="s">
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="21" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1260,9 +1209,9 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="26" t="s">
+      <c r="A7" s="26"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -1271,7 +1220,7 @@
       <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -1317,16 +1266,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="30"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1368,12 +1317,12 @@
         <v>34</v>
       </c>
       <c r="B9" s="10"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="22"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="24"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1415,12 +1364,12 @@
         <v>24</v>
       </c>
       <c r="B10" s="10"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="22"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1462,12 +1411,12 @@
         <v>27</v>
       </c>
       <c r="B11" s="10"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="18"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="16"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1509,12 +1458,12 @@
         <v>28</v>
       </c>
       <c r="B12" s="10"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="18"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="16"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1556,12 +1505,12 @@
         <v>29</v>
       </c>
       <c r="B13" s="10"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="18"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="16"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1603,12 +1552,12 @@
         <v>30</v>
       </c>
       <c r="B14" s="10"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="24"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1650,12 +1599,12 @@
         <v>35</v>
       </c>
       <c r="B15" s="10"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="22"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1697,12 +1646,12 @@
         <v>31</v>
       </c>
       <c r="B16" s="10"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="22"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1744,12 +1693,12 @@
         <v>36</v>
       </c>
       <c r="B17" s="10"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="22"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="24"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1791,12 +1740,12 @@
         <v>37</v>
       </c>
       <c r="B18" s="10"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="18"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="16"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1834,16 +1783,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1884,15 +1833,15 @@
       <c r="A20" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="25"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="19"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1933,15 +1882,15 @@
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="25"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="19"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1979,18 +1928,18 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="25"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="19"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2028,16 +1977,16 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="36"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="33"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2074,15 +2023,19 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="18"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="24"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2119,15 +2072,19 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="18"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="24"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2165,14 +2122,14 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2199,25 +2156,16 @@
       <c r="AF26"/>
       <c r="AG26"/>
       <c r="AH26"/>
-      <c r="AI26"/>
-      <c r="AJ26"/>
-      <c r="AK26"/>
-      <c r="AL26"/>
-      <c r="AM26"/>
-      <c r="AN26"/>
-      <c r="AO26"/>
-      <c r="AP26"/>
-      <c r="AQ26"/>
-    </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="18"/>
+    </row>
+    <row r="27" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2243,26 +2191,16 @@
       <c r="AE27"/>
       <c r="AF27"/>
       <c r="AG27"/>
-      <c r="AH27"/>
-      <c r="AI27"/>
-      <c r="AJ27"/>
-      <c r="AK27"/>
-      <c r="AL27"/>
-      <c r="AM27"/>
-      <c r="AN27"/>
-      <c r="AO27"/>
-      <c r="AP27"/>
-      <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="18"/>
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2289,25 +2227,16 @@
       <c r="AF28"/>
       <c r="AG28"/>
       <c r="AH28"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
-      <c r="AK28"/>
-      <c r="AL28"/>
-      <c r="AM28"/>
-      <c r="AN28"/>
-      <c r="AO28"/>
-      <c r="AP28"/>
-      <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="18"/>
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2325,34 +2254,16 @@
       <c r="W29"/>
       <c r="X29"/>
       <c r="Y29"/>
-      <c r="Z29"/>
-      <c r="AA29"/>
-      <c r="AB29"/>
-      <c r="AC29"/>
-      <c r="AD29"/>
-      <c r="AE29"/>
-      <c r="AF29"/>
-      <c r="AG29"/>
-      <c r="AH29"/>
-      <c r="AI29"/>
-      <c r="AJ29"/>
-      <c r="AK29"/>
-      <c r="AL29"/>
-      <c r="AM29"/>
-      <c r="AN29"/>
-      <c r="AO29"/>
-      <c r="AP29"/>
-      <c r="AQ29"/>
-    </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="20"/>
+    </row>
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2380,14 +2291,6 @@
       <c r="AG30"/>
       <c r="AH30"/>
       <c r="AI30"/>
-      <c r="AJ30"/>
-      <c r="AK30"/>
-      <c r="AL30"/>
-      <c r="AM30"/>
-      <c r="AN30"/>
-      <c r="AO30"/>
-      <c r="AP30"/>
-      <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
@@ -2973,10 +2876,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8699F405-6A98-4E42-A4E6-D622358F7C7F}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="448e5bc6-220e-4232-be9c-92dc25a4e4e5"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="2197ab10-882f-4df3-a7c2-cbc9019ef6c3"/>
-    <ds:schemaRef ds:uri="448e5bc6-220e-4232-be9c-92dc25a4e4e5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Stage/Bedjou Ayoub fiche de synthése.xlsx
+++ b/Stage/Bedjou Ayoub fiche de synthése.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\portefolio\wetransfer_portfolio_2025-12-01_2312\Portfolio\Stage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF59A662-CB2A-4BB3-94DB-1A3AFE1C23A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3929FEDF-1164-4062-A6F0-B11E6AE6D5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,14 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$32</definedName>
   </definedNames>
   <calcPr calcId="101716"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -102,9 +101,6 @@
 (intitulé et liste des documents et productions associés)</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -114,27 +110,15 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création Calculatrice </t>
-  </si>
-  <si>
     <t>SESSION 2026</t>
   </si>
   <si>
     <t>Centre de formation : ENC PARIS 17</t>
   </si>
   <si>
-    <t>Distance Inter-Villes</t>
-  </si>
-  <si>
     <t>Motus (Java)</t>
   </si>
   <si>
-    <t>Tri bulles /selection</t>
-  </si>
-  <si>
     <t>Plan de réseau GregCity</t>
   </si>
   <si>
@@ -147,18 +131,12 @@
     <t xml:space="preserve">19/05/2025/ au 20/06/2025 </t>
   </si>
   <si>
-    <t>Développement de mon portfolio</t>
-  </si>
-  <si>
     <t>Développement d'une petite application méteo ( HTML CSS JS avec utilisation d'une API météo)</t>
   </si>
   <si>
     <t>Développement d'un générateur de blague ( HTML CSS JS avec une API).</t>
   </si>
   <si>
-    <t>Projet Guesswhat - jeu de bridge , réalisation de tests unitaires</t>
-  </si>
-  <si>
     <t>NOM et prénom : BEDJOU Ayoub</t>
   </si>
   <si>
@@ -178,6 +156,36 @@
   </si>
   <si>
     <t>12/01/2026 au 20/02/2026</t>
+  </si>
+  <si>
+    <t>Développement de mon portfolio en HTML CSS et Javascript</t>
+  </si>
+  <si>
+    <t>Tri bulles /selection en Java</t>
+  </si>
+  <si>
+    <t>Distance Inter-Villes avec Java</t>
+  </si>
+  <si>
+    <t>N° candidat : 02541475228-001</t>
+  </si>
+  <si>
+    <t>Création Calculatrice en Java</t>
+  </si>
+  <si>
+    <t>mars 2025 à Avril 2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://github.com/Ayoub-2005/portfolio--Bedjou-Ayoub-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undercover Game : Jeu de mots entre amis dévelopement d'une interface graphique pour l'atribution des mots a tous les joueurs . Ce jeu est  dévéloppé avec Vue.js  </t>
+  </si>
+  <si>
+    <t>Mars 2026 à Avril 2026</t>
+  </si>
+  <si>
+    <t>Quiz cinématographique avec un tirage de questions aléatoire  dévéloppé avec Django</t>
   </si>
 </sst>
 </file>
@@ -616,7 +624,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -688,15 +696,48 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -728,30 +769,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1100,7 +1117,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="25.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.5703125" style="1" customWidth="1"/>
@@ -1110,56 +1127,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="27"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="46"/>
+      <c r="A3" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="30"/>
+      <c r="H3" s="36"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
+      <c r="A4" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1171,23 +1188,23 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="A5" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>20</v>
+      <c r="B6" s="45" t="s">
+        <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>0</v>
@@ -1209,8 +1226,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="46"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1266,16 +1283,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="30"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1314,9 +1331,11 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="10"/>
+        <v>38</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>43</v>
+      </c>
       <c r="C9" s="14"/>
       <c r="D9" s="15"/>
       <c r="E9" s="23"/>
@@ -1361,9 +1380,11 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="B10" s="26">
+        <v>45697</v>
+      </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
@@ -1408,9 +1429,11 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="B11" s="26">
+        <v>45734</v>
+      </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
@@ -1455,9 +1478,11 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="10"/>
+        <v>24</v>
+      </c>
+      <c r="B12" s="26">
+        <v>45697</v>
+      </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
@@ -1502,9 +1527,11 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="10"/>
+        <v>39</v>
+      </c>
+      <c r="B13" s="26">
+        <v>45734</v>
+      </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -1549,9 +1576,11 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="B14" s="27">
+        <v>45627</v>
+      </c>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
       <c r="E14" s="15"/>
@@ -1596,9 +1625,11 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="10"/>
+        <v>29</v>
+      </c>
+      <c r="B15" s="26">
+        <v>45758</v>
+      </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
@@ -1643,9 +1674,11 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="B16" s="26">
+        <v>45646</v>
+      </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
@@ -1690,9 +1723,11 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="10"/>
+        <v>30</v>
+      </c>
+      <c r="B17" s="26">
+        <v>45741</v>
+      </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
@@ -1735,17 +1770,19 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="10"/>
+        <v>45</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>46</v>
+      </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
-      <c r="F18" s="23"/>
+      <c r="F18" s="17"/>
       <c r="G18" s="23"/>
-      <c r="H18" s="16"/>
+      <c r="H18" s="24"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1782,17 +1819,19 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="24"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1829,19 +1868,17 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="19"/>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="44"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1878,12 +1915,12 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="81" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>40</v>
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C21" s="23"/>
       <c r="D21" s="23"/>
@@ -1927,18 +1964,18 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>41</v>
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
-      <c r="E22" s="15"/>
+      <c r="E22" s="17"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="15"/>
+      <c r="G22" s="23"/>
       <c r="H22" s="19"/>
       <c r="I22"/>
       <c r="J22"/>
@@ -1976,17 +2013,19 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="33"/>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="19"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2023,19 +2062,17 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="24"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2074,12 +2111,12 @@
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="10"/>
       <c r="D25" s="15"/>
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
@@ -2122,14 +2159,18 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
+      <c r="A26" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2293,14 +2334,14 @@
       <c r="AI30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="5"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2338,14 +2379,14 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32"/>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
+      <c r="A32" s="5"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2559,16 +2600,7 @@
     <row r="75" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="76" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-    </row>
+    <row r="78" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="79" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
@@ -2601,18 +2633,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2623,15 +2655,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="2197ab10-882f-4df3-a7c2-cbc9019ef6c3" xsi:nil="true"/>
@@ -2640,6 +2663,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2866,14 +2898,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCE846E6-82B3-4E26-AE12-6B4ADF4F7EBF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8699F405-6A98-4E42-A4E6-D622358F7C7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -2886,6 +2910,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="2197ab10-882f-4df3-a7c2-cbc9019ef6c3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCE846E6-82B3-4E26-AE12-6B4ADF4F7EBF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Stage/Bedjou Ayoub fiche de synthése.xlsx
+++ b/Stage/Bedjou Ayoub fiche de synthése.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\new Portfolio\portfolio--Bedjou-Ayoub-\Stage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3929FEDF-1164-4062-A6F0-B11E6AE6D5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98711DCF-A6DE-4A46-A177-9C5EDD72A556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -705,9 +705,48 @@
     <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -730,45 +769,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1127,56 +1127,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="35" t="s">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="36"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="49"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
       <c r="F4" s="12" t="s">
         <v>8</v>
       </c>
@@ -1188,22 +1188,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="49"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="37" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1226,8 +1226,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38"/>
-      <c r="B7" s="46"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="38"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1283,16 +1283,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1869,16 +1869,16 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="44"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2062,17 +2062,17 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="42" t="s">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2109,7 +2109,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>36</v>
       </c>
@@ -2158,7 +2158,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>35</v>
       </c>
@@ -2633,6 +2633,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2640,11 +2645,6 @@
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2655,6 +2655,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="2197ab10-882f-4df3-a7c2-cbc9019ef6c3" xsi:nil="true"/>
@@ -2663,15 +2672,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2898,6 +2898,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCE846E6-82B3-4E26-AE12-6B4ADF4F7EBF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8699F405-6A98-4E42-A4E6-D622358F7C7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -2910,14 +2918,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="2197ab10-882f-4df3-a7c2-cbc9019ef6c3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCE846E6-82B3-4E26-AE12-6B4ADF4F7EBF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
